--- a/artfynd/A 13314-2026 artfynd.xlsx
+++ b/artfynd/A 13314-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121350170</v>
+        <v>121350169</v>
       </c>
       <c r="B2" t="n">
-        <v>58216</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
@@ -728,10 +723,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>606439</v>
+        <v>606257</v>
       </c>
       <c r="R2" t="n">
-        <v>6753916</v>
+        <v>6753918</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -758,12 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-08-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121350251</v>
+        <v>121350170</v>
       </c>
       <c r="B3" t="n">
-        <v>56318</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -811,21 +801,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208255</v>
+        <v>208249</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsödla</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Zootoca vivipara</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Jacquin, 1787)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -833,16 +823,25 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hamrånge, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>606443</v>
+        <v>606439</v>
       </c>
       <c r="R3" t="n">
-        <v>6753930</v>
+        <v>6753916</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,6 +882,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,15 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121350438</v>
+        <v>121350251</v>
       </c>
       <c r="B4" t="n">
-        <v>98030</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56884</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -921,21 +916,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>208255</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Skogsödla</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Zootoca vivipara</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Jacquin, 1787)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -943,21 +938,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hamrånge, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>606247</v>
+        <v>606443</v>
       </c>
       <c r="R4" t="n">
-        <v>6753881</v>
+        <v>6753930</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,12 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-08-14</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,6 +1003,336 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121350438</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hamrånge, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>606247</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6753881</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121350320</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hamrånge, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>606695</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6754029</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121350301</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hamrånge, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>606250</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6753916</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hamrånge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-08-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Tony Svensson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
         <is>
           <t>Ecogain</t>
         </is>
